--- a/Team-Data/2013-14/1-5-2013-14.xlsx
+++ b/Team-Data/2013-14/1-5-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -745,7 +812,7 @@
         <v>11</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
@@ -754,31 +821,31 @@
         <v>6</v>
       </c>
       <c r="AI2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK2" t="n">
         <v>8</v>
       </c>
       <c r="AL2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN2" t="n">
         <v>9</v>
       </c>
       <c r="AO2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AP2" t="n">
         <v>21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
         <v>29</v>
@@ -799,7 +866,7 @@
         <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY2" t="n">
         <v>15</v>
@@ -814,7 +881,7 @@
         <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E3" t="n">
         <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>0.382</v>
+        <v>0.394</v>
       </c>
       <c r="H3" t="n">
         <v>48</v>
@@ -861,40 +928,40 @@
         <v>36.2</v>
       </c>
       <c r="J3" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K3" t="n">
         <v>0.446</v>
       </c>
       <c r="L3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="M3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="O3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="P3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="R3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>42</v>
+      </c>
+      <c r="U3" t="n">
         <v>18.9</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="O3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="P3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="R3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="S3" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="U3" t="n">
-        <v>19.1</v>
       </c>
       <c r="V3" t="n">
         <v>16</v>
@@ -909,7 +976,7 @@
         <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="AA3" t="n">
         <v>18.6</v>
@@ -918,16 +985,16 @@
         <v>94.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2.7</v>
+        <v>-2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE3" t="n">
         <v>22</v>
       </c>
       <c r="AF3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG3" t="n">
         <v>22</v>
@@ -936,7 +1003,7 @@
         <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ3" t="n">
         <v>25</v>
@@ -945,22 +1012,22 @@
         <v>15</v>
       </c>
       <c r="AL3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AM3" t="n">
         <v>25</v>
       </c>
       <c r="AN3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
         <v>20</v>
@@ -975,7 +1042,7 @@
         <v>29</v>
       </c>
       <c r="AV3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
         <v>27</v>
@@ -984,7 +1051,7 @@
         <v>14</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>20</v>
@@ -996,7 +1063,7 @@
         <v>26</v>
       </c>
       <c r="BC3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -1103,19 +1170,19 @@
         <v>-5</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG4" t="n">
         <v>23</v>
       </c>
       <c r="AH4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1124,7 +1191,7 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
@@ -1142,7 +1209,7 @@
         <v>4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
         <v>27</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -1285,13 +1352,13 @@
         <v>-2.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
         <v>19</v>
@@ -1360,7 +1427,7 @@
         <v>27</v>
       </c>
       <c r="BC5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -1467,16 +1534,16 @@
         <v>-0.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF6" t="n">
         <v>17</v>
       </c>
       <c r="AG6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH6" t="n">
         <v>7</v>
@@ -1488,7 +1555,7 @@
         <v>26</v>
       </c>
       <c r="AK6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL6" t="n">
         <v>28</v>
@@ -1500,16 +1567,16 @@
         <v>29</v>
       </c>
       <c r="AO6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP6" t="n">
         <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
         <v>13</v>
@@ -1518,7 +1585,7 @@
         <v>8</v>
       </c>
       <c r="AU6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AV6" t="n">
         <v>27</v>
@@ -1533,7 +1600,7 @@
         <v>29</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA6" t="n">
         <v>8</v>
@@ -1542,7 +1609,7 @@
         <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -1571,28 +1638,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7" t="n">
         <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G7" t="n">
-        <v>0.324</v>
+        <v>0.333</v>
       </c>
       <c r="H7" t="n">
         <v>49.2</v>
       </c>
       <c r="I7" t="n">
-        <v>35.9</v>
+        <v>36.2</v>
       </c>
       <c r="J7" t="n">
-        <v>85.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0.42</v>
+        <v>0.422</v>
       </c>
       <c r="L7" t="n">
         <v>7</v>
@@ -1601,7 +1668,7 @@
         <v>19.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O7" t="n">
         <v>16.1</v>
@@ -1610,118 +1677,118 @@
         <v>21.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.755</v>
+        <v>0.751</v>
       </c>
       <c r="R7" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S7" t="n">
         <v>32.2</v>
       </c>
       <c r="T7" t="n">
-        <v>44.3</v>
+        <v>44.2</v>
       </c>
       <c r="U7" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="V7" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W7" t="n">
         <v>7.1</v>
       </c>
       <c r="X7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="AA7" t="n">
         <v>19.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="AC7" t="n">
         <v>-5.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
         <v>25</v>
       </c>
       <c r="AF7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AG7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH7" t="n">
         <v>1</v>
       </c>
       <c r="AI7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AJ7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM7" t="n">
         <v>23</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP7" t="n">
         <v>20</v>
       </c>
       <c r="AQ7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS7" t="n">
         <v>15</v>
       </c>
       <c r="AT7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AW7" t="n">
         <v>23</v>
       </c>
       <c r="AX7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA7" t="n">
         <v>21</v>
       </c>
       <c r="BB7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -1753,85 +1820,85 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E8" t="n">
         <v>19</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.576</v>
       </c>
       <c r="H8" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="I8" t="n">
-        <v>39.2</v>
+        <v>39.4</v>
       </c>
       <c r="J8" t="n">
-        <v>84.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.466</v>
+        <v>0.467</v>
       </c>
       <c r="L8" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="M8" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.371</v>
+        <v>0.376</v>
       </c>
       <c r="O8" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="P8" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.803</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T8" t="n">
-        <v>40.5</v>
+        <v>40.7</v>
       </c>
       <c r="U8" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="V8" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W8" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="X8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y8" t="n">
         <v>3.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA8" t="n">
         <v>18.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>102.9</v>
+        <v>103.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
         <v>10</v>
@@ -1846,10 +1913,10 @@
         <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
@@ -1861,10 +1928,10 @@
         <v>10</v>
       </c>
       <c r="AN8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP8" t="n">
         <v>28</v>
@@ -1876,22 +1943,22 @@
         <v>24</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT8" t="n">
         <v>27</v>
       </c>
       <c r="AU8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV8" t="n">
         <v>8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>7</v>
       </c>
       <c r="AW8" t="n">
         <v>2</v>
       </c>
       <c r="AX8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1903,10 +1970,10 @@
         <v>29</v>
       </c>
       <c r="BB8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -1935,112 +2002,112 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
         <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>0.485</v>
+        <v>0.469</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>37.7</v>
+        <v>37.3</v>
       </c>
       <c r="J9" t="n">
-        <v>84.7</v>
+        <v>84.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.446</v>
+        <v>0.442</v>
       </c>
       <c r="L9" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="M9" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.348</v>
+        <v>0.346</v>
       </c>
       <c r="O9" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="P9" t="n">
         <v>25.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.73</v>
+        <v>0.728</v>
       </c>
       <c r="R9" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S9" t="n">
-        <v>33.1</v>
+        <v>32.9</v>
       </c>
       <c r="T9" t="n">
-        <v>45.8</v>
+        <v>45.4</v>
       </c>
       <c r="U9" t="n">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="V9" t="n">
         <v>15.1</v>
       </c>
       <c r="W9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="X9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y9" t="n">
         <v>5.9</v>
       </c>
-      <c r="Y9" t="n">
-        <v>5.8</v>
-      </c>
       <c r="Z9" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA9" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="AD9" t="n">
         <v>21</v>
       </c>
-      <c r="AB9" t="n">
-        <v>101.4</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>16</v>
-      </c>
       <c r="AE9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
         <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AK9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AM9" t="n">
         <v>15</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>13</v>
       </c>
       <c r="AN9" t="n">
         <v>19</v>
@@ -2058,13 +2125,13 @@
         <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AU9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV9" t="n">
         <v>13</v>
@@ -2082,13 +2149,13 @@
         <v>24</v>
       </c>
       <c r="BA9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -2117,64 +2184,64 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" t="n">
         <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G10" t="n">
-        <v>0.412</v>
+        <v>0.424</v>
       </c>
       <c r="H10" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I10" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J10" t="n">
         <v>85.8</v>
       </c>
       <c r="K10" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L10" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M10" t="n">
         <v>19.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.318</v>
+        <v>0.321</v>
       </c>
       <c r="O10" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="P10" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.661</v>
+        <v>0.665</v>
       </c>
       <c r="R10" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="S10" t="n">
         <v>29.8</v>
       </c>
       <c r="T10" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
       <c r="U10" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V10" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X10" t="n">
         <v>5.2</v>
@@ -2186,19 +2253,19 @@
         <v>20.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>99.40000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3</v>
+        <v>-2.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF10" t="n">
         <v>19</v>
@@ -2207,13 +2274,13 @@
         <v>20</v>
       </c>
       <c r="AH10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK10" t="n">
         <v>14</v>
@@ -2228,7 +2295,7 @@
         <v>30</v>
       </c>
       <c r="AO10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -2240,37 +2307,37 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ10" t="n">
         <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BB10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -2299,31 +2366,31 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.639</v>
+        <v>0.629</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="J11" t="n">
         <v>84.3</v>
       </c>
       <c r="K11" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L11" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="M11" t="n">
         <v>24.1</v>
@@ -2332,73 +2399,73 @@
         <v>0.392</v>
       </c>
       <c r="O11" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="P11" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.73</v>
+        <v>0.727</v>
       </c>
       <c r="R11" t="n">
         <v>11.1</v>
       </c>
       <c r="S11" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="T11" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
       <c r="U11" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V11" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="W11" t="n">
         <v>7.9</v>
       </c>
       <c r="X11" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y11" t="n">
         <v>4.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.6</v>
+        <v>103.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF11" t="n">
         <v>7</v>
       </c>
       <c r="AG11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ11" t="n">
         <v>8</v>
       </c>
       <c r="AK11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL11" t="n">
         <v>3</v>
@@ -2410,7 +2477,7 @@
         <v>3</v>
       </c>
       <c r="AO11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
         <v>19</v>
@@ -2425,10 +2492,10 @@
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
         <v>29</v>
@@ -2437,22 +2504,22 @@
         <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -2559,22 +2626,22 @@
         <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF12" t="n">
         <v>7</v>
       </c>
       <c r="AG12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH12" t="n">
         <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AJ12" t="n">
         <v>28</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
@@ -2619,7 +2686,7 @@
         <v>19</v>
       </c>
       <c r="AX12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY12" t="n">
         <v>20</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -2663,58 +2730,58 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F13" t="n">
         <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
       </c>
       <c r="I13" t="n">
-        <v>36.1</v>
+        <v>36.3</v>
       </c>
       <c r="J13" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0.456</v>
+        <v>0.459</v>
       </c>
       <c r="L13" t="n">
         <v>7.3</v>
       </c>
       <c r="M13" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.361</v>
+        <v>0.362</v>
       </c>
       <c r="O13" t="n">
         <v>18.2</v>
       </c>
       <c r="P13" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="R13" t="n">
         <v>9.5</v>
       </c>
       <c r="S13" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="T13" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="U13" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V13" t="n">
         <v>15.7</v>
@@ -2723,25 +2790,25 @@
         <v>7.5</v>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z13" t="n">
         <v>19.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.59999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2753,22 +2820,22 @@
         <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AJ13" t="n">
         <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL13" t="n">
         <v>19</v>
       </c>
       <c r="AM13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN13" t="n">
         <v>12</v>
@@ -2783,7 +2850,7 @@
         <v>5</v>
       </c>
       <c r="AR13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS13" t="n">
         <v>3</v>
@@ -2798,13 +2865,13 @@
         <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ13" t="n">
         <v>9</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -2935,7 +3002,7 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI14" t="n">
         <v>13</v>
@@ -2944,7 +3011,7 @@
         <v>22</v>
       </c>
       <c r="AK14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL14" t="n">
         <v>13</v>
@@ -2983,7 +3050,7 @@
         <v>11</v>
       </c>
       <c r="AX14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AY14" t="n">
         <v>2</v>
@@ -2998,7 +3065,7 @@
         <v>6</v>
       </c>
       <c r="BC14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>0.412</v>
+        <v>0.424</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="J15" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K15" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="M15" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.365</v>
+        <v>0.37</v>
       </c>
       <c r="O15" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="P15" t="n">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.742</v>
+        <v>0.74</v>
       </c>
       <c r="R15" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="S15" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T15" t="n">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
       <c r="U15" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V15" t="n">
         <v>15.2</v>
@@ -3087,28 +3154,28 @@
         <v>6.6</v>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.7</v>
+        <v>99.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-4.5</v>
+        <v>-3.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF15" t="n">
         <v>19</v>
@@ -3129,7 +3196,7 @@
         <v>22</v>
       </c>
       <c r="AL15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM15" t="n">
         <v>4</v>
@@ -3138,10 +3205,10 @@
         <v>11</v>
       </c>
       <c r="AO15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ15" t="n">
         <v>23</v>
@@ -3150,16 +3217,16 @@
         <v>23</v>
       </c>
       <c r="AS15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
         <v>12</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW15" t="n">
         <v>28</v>
@@ -3168,19 +3235,19 @@
         <v>4</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -3209,37 +3276,37 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F16" t="n">
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>0.455</v>
+        <v>0.438</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J16" t="n">
-        <v>82.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="M16" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="N16" t="n">
-        <v>0.349</v>
+        <v>0.343</v>
       </c>
       <c r="O16" t="n">
         <v>16</v>
@@ -3248,25 +3315,25 @@
         <v>21.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.755</v>
+        <v>0.753</v>
       </c>
       <c r="R16" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="S16" t="n">
-        <v>30.8</v>
+        <v>30.5</v>
       </c>
       <c r="T16" t="n">
-        <v>43.2</v>
+        <v>42.7</v>
       </c>
       <c r="U16" t="n">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="V16" t="n">
         <v>13.8</v>
       </c>
       <c r="W16" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X16" t="n">
         <v>4</v>
@@ -3275,37 +3342,37 @@
         <v>5.8</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA16" t="n">
         <v>19.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>95.7</v>
+        <v>95.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>-1.3</v>
+        <v>-2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AF16" t="n">
         <v>17</v>
       </c>
       <c r="AG16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH16" t="n">
         <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="n">
         <v>13</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
         <v>22</v>
@@ -3326,25 +3393,25 @@
         <v>22</v>
       </c>
       <c r="AQ16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR16" t="n">
         <v>6</v>
       </c>
       <c r="AS16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT16" t="n">
         <v>21</v>
       </c>
-      <c r="AT16" t="n">
-        <v>13</v>
-      </c>
       <c r="AU16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV16" t="n">
         <v>4</v>
       </c>
       <c r="AW16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX16" t="n">
         <v>27</v>
@@ -3359,10 +3426,10 @@
         <v>22</v>
       </c>
       <c r="BB16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" t="n">
         <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>0.765</v>
+        <v>0.758</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3409,79 +3476,79 @@
         <v>39.2</v>
       </c>
       <c r="J17" t="n">
-        <v>76.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.511</v>
+        <v>0.512</v>
       </c>
       <c r="L17" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.384</v>
+        <v>0.386</v>
       </c>
       <c r="O17" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="P17" t="n">
         <v>24.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.76</v>
+        <v>0.757</v>
       </c>
       <c r="R17" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="S17" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T17" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="U17" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="V17" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W17" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X17" t="n">
         <v>4.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AA17" t="n">
         <v>21.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>104.8</v>
+        <v>104.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF17" t="n">
         <v>3</v>
       </c>
       <c r="AG17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI17" t="n">
         <v>6</v>
@@ -3493,16 +3560,16 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AN17" t="n">
         <v>4</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
@@ -3529,16 +3596,16 @@
         <v>1</v>
       </c>
       <c r="AX17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-7.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3681,7 +3748,7 @@
         <v>18</v>
       </c>
       <c r="AN18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="n">
         <v>26</v>
@@ -3705,7 +3772,7 @@
         <v>18</v>
       </c>
       <c r="AV18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW18" t="n">
         <v>24</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -3833,19 +3900,19 @@
         <v>4</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AE19" t="n">
         <v>12</v>
       </c>
       <c r="AF19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
         <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI19" t="n">
         <v>9</v>
@@ -3881,13 +3948,13 @@
         <v>16</v>
       </c>
       <c r="AT19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -4015,16 +4082,16 @@
         <v>-0.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
         <v>7</v>
@@ -4039,7 +4106,7 @@
         <v>12</v>
       </c>
       <c r="AL20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM20" t="n">
         <v>27</v>
@@ -4051,16 +4118,16 @@
         <v>15</v>
       </c>
       <c r="AP20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR20" t="n">
         <v>3</v>
       </c>
       <c r="AS20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT20" t="n">
         <v>12</v>
@@ -4078,13 +4145,13 @@
         <v>2</v>
       </c>
       <c r="AY20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ20" t="n">
         <v>22</v>
       </c>
       <c r="BA20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB20" t="n">
         <v>13</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F21" t="n">
         <v>22</v>
       </c>
       <c r="G21" t="n">
-        <v>0.333</v>
+        <v>0.313</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
@@ -4137,85 +4204,85 @@
         <v>36.1</v>
       </c>
       <c r="J21" t="n">
-        <v>83.3</v>
+        <v>83.5</v>
       </c>
       <c r="K21" t="n">
-        <v>0.433</v>
+        <v>0.432</v>
       </c>
       <c r="L21" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>24.3</v>
+        <v>24.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="O21" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="P21" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.766</v>
+        <v>0.765</v>
       </c>
       <c r="R21" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S21" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="T21" t="n">
-        <v>39.5</v>
+        <v>39.3</v>
       </c>
       <c r="U21" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V21" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="W21" t="n">
         <v>8.6</v>
       </c>
       <c r="X21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3.7</v>
+        <v>-4.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF21" t="n">
         <v>25</v>
       </c>
       <c r="AG21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AJ21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AK21" t="n">
         <v>25</v>
@@ -4233,10 +4300,10 @@
         <v>30</v>
       </c>
       <c r="AP21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR21" t="n">
         <v>19</v>
@@ -4248,7 +4315,7 @@
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
@@ -4257,22 +4324,22 @@
         <v>10</v>
       </c>
       <c r="AX21" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AY21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AZ21" t="n">
         <v>29</v>
       </c>
       <c r="BA21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC21" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -4301,28 +4368,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F22" t="n">
         <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>0.794</v>
+        <v>0.788</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="J22" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.472</v>
+        <v>0.471</v>
       </c>
       <c r="L22" t="n">
         <v>6.9</v>
@@ -4331,55 +4398,55 @@
         <v>19.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.355</v>
+        <v>0.351</v>
       </c>
       <c r="O22" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="P22" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.819</v>
+        <v>0.82</v>
       </c>
       <c r="R22" t="n">
         <v>10.7</v>
       </c>
       <c r="S22" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="T22" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
       <c r="U22" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="V22" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="W22" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X22" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Y22" t="n">
         <v>3.9</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>106</v>
+        <v>105.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4391,13 +4458,13 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI22" t="n">
         <v>8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK22" t="n">
         <v>4</v>
@@ -4409,7 +4476,7 @@
         <v>24</v>
       </c>
       <c r="AN22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AO22" t="n">
         <v>3</v>
@@ -4433,7 +4500,7 @@
         <v>13</v>
       </c>
       <c r="AV22" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AW22" t="n">
         <v>14</v>
@@ -4442,10 +4509,10 @@
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
         <v>13</v>
@@ -4454,7 +4521,7 @@
         <v>3</v>
       </c>
       <c r="BC22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -4561,13 +4628,13 @@
         <v>-3.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AE23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF23" t="n">
         <v>28</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>27</v>
       </c>
       <c r="AG23" t="n">
         <v>29</v>
@@ -4579,13 +4646,13 @@
         <v>20</v>
       </c>
       <c r="AJ23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM23" t="n">
         <v>16</v>
@@ -4600,7 +4667,7 @@
         <v>23</v>
       </c>
       <c r="AQ23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR23" t="n">
         <v>28</v>
@@ -4615,19 +4682,19 @@
         <v>19</v>
       </c>
       <c r="AV23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW23" t="n">
         <v>16</v>
       </c>
       <c r="AX23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY23" t="n">
         <v>23</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA23" t="n">
         <v>28</v>
@@ -4636,7 +4703,7 @@
         <v>22</v>
       </c>
       <c r="BC23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -4743,13 +4810,13 @@
         <v>-7.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
         <v>23</v>
       </c>
       <c r="AF24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG24" t="n">
         <v>23</v>
@@ -4764,10 +4831,10 @@
         <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM24" t="n">
         <v>11</v>
@@ -4776,7 +4843,7 @@
         <v>28</v>
       </c>
       <c r="AO24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP24" t="n">
         <v>15</v>
@@ -4791,7 +4858,7 @@
         <v>5</v>
       </c>
       <c r="AT24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU24" t="n">
         <v>10</v>
@@ -4812,10 +4879,10 @@
         <v>21</v>
       </c>
       <c r="BA24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC24" t="n">
         <v>28</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>3.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
@@ -4943,7 +5010,7 @@
         <v>12</v>
       </c>
       <c r="AJ25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK25" t="n">
         <v>9</v>
@@ -4955,7 +5022,7 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
         <v>14</v>
@@ -4964,7 +5031,7 @@
         <v>13</v>
       </c>
       <c r="AQ25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR25" t="n">
         <v>14</v>
@@ -4979,16 +5046,16 @@
         <v>28</v>
       </c>
       <c r="AV25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX25" t="n">
         <v>8</v>
       </c>
       <c r="AY25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ25" t="n">
         <v>19</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5177,7 @@
         <v>6</v>
       </c>
       <c r="AE26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF26" t="n">
         <v>3</v>
@@ -5119,7 +5186,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
@@ -5128,7 +5195,7 @@
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL26" t="n">
         <v>1</v>
@@ -5155,7 +5222,7 @@
         <v>6</v>
       </c>
       <c r="AT26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU26" t="n">
         <v>3</v>
@@ -5176,7 +5243,7 @@
         <v>3</v>
       </c>
       <c r="BA26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB26" t="n">
         <v>1</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -5289,16 +5356,16 @@
         <v>-3.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF27" t="n">
         <v>25</v>
       </c>
       <c r="AG27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH27" t="n">
         <v>10</v>
@@ -5310,19 +5377,19 @@
         <v>13</v>
       </c>
       <c r="AK27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="n">
         <v>23</v>
       </c>
       <c r="AM27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN27" t="n">
         <v>24</v>
       </c>
       <c r="AO27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP27" t="n">
         <v>8</v>
@@ -5334,13 +5401,13 @@
         <v>11</v>
       </c>
       <c r="AS27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV27" t="n">
         <v>12</v>
@@ -5361,10 +5428,10 @@
         <v>5</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5541,7 @@
         <v>6</v>
       </c>
       <c r="AE28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF28" t="n">
         <v>3</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5507,13 +5574,13 @@
         <v>29</v>
       </c>
       <c r="AP28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS28" t="n">
         <v>7</v>
@@ -5531,7 +5598,7 @@
         <v>15</v>
       </c>
       <c r="AX28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -5546,7 +5613,7 @@
         <v>7</v>
       </c>
       <c r="BC28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E29" t="n">
         <v>16</v>
       </c>
       <c r="F29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5</v>
+        <v>0.516</v>
       </c>
       <c r="H29" t="n">
         <v>48.8</v>
       </c>
       <c r="I29" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J29" t="n">
-        <v>82.3</v>
+        <v>82.5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.438</v>
+        <v>0.436</v>
       </c>
       <c r="L29" t="n">
         <v>7.7</v>
@@ -5605,55 +5672,55 @@
         <v>21.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="O29" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="P29" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.775</v>
+        <v>0.78</v>
       </c>
       <c r="R29" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S29" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T29" t="n">
-        <v>42.5</v>
+        <v>42.8</v>
       </c>
       <c r="U29" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V29" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W29" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z29" t="n">
         <v>22.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5668,10 +5735,10 @@
         <v>5</v>
       </c>
       <c r="AI29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK29" t="n">
         <v>23</v>
@@ -5683,25 +5750,25 @@
         <v>12</v>
       </c>
       <c r="AN29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP29" t="n">
         <v>9</v>
       </c>
       <c r="AQ29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR29" t="n">
         <v>10</v>
       </c>
       <c r="AS29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT29" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AU29" t="n">
         <v>26</v>
@@ -5710,10 +5777,10 @@
         <v>11</v>
       </c>
       <c r="AW29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX29" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AY29" t="n">
         <v>17</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -5859,19 +5926,19 @@
         <v>26</v>
       </c>
       <c r="AL30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM30" t="n">
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO30" t="n">
         <v>25</v>
       </c>
       <c r="AP30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ30" t="n">
         <v>16</v>
@@ -5880,7 +5947,7 @@
         <v>12</v>
       </c>
       <c r="AS30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT30" t="n">
         <v>25</v>
@@ -5892,7 +5959,7 @@
         <v>16</v>
       </c>
       <c r="AW30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX30" t="n">
         <v>13</v>
@@ -5904,7 +5971,7 @@
         <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E31" t="n">
         <v>14</v>
       </c>
       <c r="F31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G31" t="n">
-        <v>0.452</v>
+        <v>0.467</v>
       </c>
       <c r="H31" t="n">
         <v>49</v>
@@ -5957,31 +6024,31 @@
         <v>37.5</v>
       </c>
       <c r="J31" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K31" t="n">
         <v>0.446</v>
       </c>
       <c r="L31" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0.383</v>
+        <v>0.386</v>
       </c>
       <c r="O31" t="n">
         <v>15.4</v>
       </c>
       <c r="P31" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.75</v>
+        <v>0.744</v>
       </c>
       <c r="R31" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S31" t="n">
         <v>31.2</v>
@@ -5993,55 +6060,55 @@
         <v>23</v>
       </c>
       <c r="V31" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W31" t="n">
         <v>8.6</v>
       </c>
       <c r="X31" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>-1.6</v>
+        <v>-1.1</v>
       </c>
       <c r="AD31" t="n">
         <v>30</v>
       </c>
       <c r="AE31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH31" t="n">
         <v>4</v>
       </c>
       <c r="AI31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ31" t="n">
         <v>10</v>
       </c>
       <c r="AK31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM31" t="n">
         <v>14</v>
@@ -6053,16 +6120,16 @@
         <v>28</v>
       </c>
       <c r="AP31" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AQ31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR31" t="n">
         <v>13</v>
       </c>
       <c r="AS31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT31" t="n">
         <v>22</v>
@@ -6077,22 +6144,22 @@
         <v>9</v>
       </c>
       <c r="AX31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AY31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB31" t="n">
         <v>19</v>
       </c>
       <c r="BC31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-5-2013-14</t>
+          <t>2014-01-05</t>
         </is>
       </c>
     </row>
